--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488260_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488260_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4241</v>
+        <v>3.6955</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3484</v>
+        <v>3.2504</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0757</v>
+        <v>0.445</v>
       </c>
       <c r="G2" t="n">
         <v>2.16</v>
@@ -610,13 +610,13 @@
         <v>1.8529</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7436</v>
+        <v>1.015</v>
       </c>
       <c r="T2" t="n">
-        <v>0.873</v>
+        <v>0.7751</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1294</v>
+        <v>0.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.4469</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8194</v>
+        <v>1.1439</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1089</v>
+        <v>1.3595</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2894</v>
+        <v>-0.2156</v>
       </c>
       <c r="G3" t="n">
         <v>1.0828</v>
@@ -688,13 +688,13 @@
         <v>1.4823</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0813</v>
+        <v>0.2431</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.041</v>
+        <v>0.2096</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0403</v>
+        <v>0.0335</v>
       </c>
       <c r="V3" t="n">
         <v>0.1886</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7072000000000001</v>
+        <v>0.5153</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7534</v>
+        <v>-0.1154</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.0462</v>
+        <v>0.6307</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7553</v>
+        <v>0.1592</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3527</v>
+        <v>2.2882</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5974</v>
+        <v>-2.129</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2449</v>
+        <v>0.5413</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1205</v>
+        <v>1.7949</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1244</v>
+        <v>-1.2536</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4897</v>
+        <v>-0.3821</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2322</v>
+        <v>0.4933</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7219</v>
+        <v>-0.8754</v>
       </c>
       <c r="P4" t="n">
         <v>0.7411</v>
@@ -766,28 +766,28 @@
         <v>0.7411</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4129</v>
+        <v>0.2444</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5084</v>
+        <v>-0.0267</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0955</v>
+        <v>0.2711</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.2022</v>
+        <v>-0.6294</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2022</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GEDEAO YIMBU</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0704</v>
+        <v>-0.0265</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3594</v>
+        <v>1.872</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.289</v>
+        <v>-1.8985</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7904</v>
+        <v>0.7553</v>
       </c>
       <c r="H5" t="n">
-        <v>4.0239</v>
+        <v>1.3527</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2335</v>
+        <v>-0.5974</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3615</v>
+        <v>1.2449</v>
       </c>
       <c r="K5" t="n">
-        <v>4.4184</v>
+        <v>1.1205</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0569</v>
+        <v>0.1244</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-0.4897</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3945</v>
+        <v>0.2322</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1766</v>
+        <v>-0.7219</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>0.7411</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3508</v>
+        <v>0.6793</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7047</v>
+        <v>0.6271</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6461</v>
+        <v>0.0522</v>
       </c>
       <c r="V5" t="n">
-        <v>-4.218</v>
+        <v>-2.2022</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0011</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.2169</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0231</v>
+        <v>-0.217</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.703</v>
+        <v>2.7896</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6798999999999999</v>
+        <v>-3.0066</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1592</v>
+        <v>2.2301</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2882</v>
+        <v>-1.3365</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.129</v>
+        <v>3.5665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5413</v>
+        <v>3.6632</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7949</v>
+        <v>-0.318</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2536</v>
+        <v>3.9812</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3821</v>
+        <v>-1.4331</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4933</v>
+        <v>-1.0184</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8754</v>
+        <v>-0.4147</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7411</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.294</v>
+        <v>0.1262</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6143</v>
+        <v>0.0529</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3203</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6294</v>
+        <v>-2.2027</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0005</v>
+        <v>-2.2027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>M. MOLINA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4183</v>
+        <v>-1.1989</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5391</v>
+        <v>0.4374</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9574</v>
+        <v>-1.6363</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2301</v>
+        <v>-0.8835</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3365</v>
+        <v>-1.0556</v>
       </c>
       <c r="I7" t="n">
-        <v>3.5665</v>
+        <v>0.172</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6632</v>
+        <v>-0.547</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.318</v>
+        <v>-0.5884</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9812</v>
+        <v>0.0415</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4331</v>
+        <v>-0.3366</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0184</v>
+        <v>-0.4671</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4147</v>
+        <v>0.1306</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3706</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.1853</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0751</v>
+        <v>0.7402</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1977</v>
+        <v>0.6519</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1226</v>
+        <v>0.0883</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.2027</v>
+        <v>-0.3144</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2027</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MOLINA LOPEZ</t>
+          <t>M. GEDEAO YIMBU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1995</v>
+        <v>-1.6645</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5353</v>
+        <v>1.0431</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7348</v>
+        <v>-2.7076</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8835</v>
+        <v>2.7904</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0556</v>
+        <v>4.0239</v>
       </c>
       <c r="I8" t="n">
-        <v>0.172</v>
+        <v>-1.2335</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.547</v>
+        <v>3.3615</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5884</v>
+        <v>4.4184</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0415</v>
+        <v>-1.0569</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3366</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4671</v>
+        <v>-0.3945</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1306</v>
+        <v>-0.1766</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7411</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7397</v>
+        <v>1.616</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7499</v>
+        <v>1.3884</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0102</v>
+        <v>0.2275</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3144</v>
+        <v>-4.218</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2589</v>
+        <v>-0.0011</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5733</v>
+        <v>-4.2169</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6868</v>
+        <v>-2.4575</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.0107</v>
+        <v>-2.6829</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3239</v>
+        <v>0.2255</v>
       </c>
       <c r="G9" t="n">
         <v>-1.7036</v>
@@ -1156,13 +1156,13 @@
         <v>1.8529</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.2284</v>
+        <v>0.0009</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3467</v>
+        <v>-0.0189</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1183</v>
+        <v>0.0199</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7548</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9697</v>
+        <v>-5.793</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.967</v>
+        <v>-3.7164</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0027</v>
+        <v>-2.0765</v>
       </c>
       <c r="G10" t="n">
         <v>-2.8663</v>
@@ -1234,13 +1234,13 @@
         <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1696</v>
+        <v>0.3463</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1816</v>
+        <v>0.4321</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.012</v>
+        <v>-0.0858</v>
       </c>
       <c r="V10" t="n">
         <v>-3.273</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.276299999999999</v>
+        <v>-6.002700000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>3.9638</v>
+        <v>4.2373</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.24</v>
+        <v>-10.2399</v>
       </c>
       <c r="G11" t="n">
         <v>3.7244</v>
       </c>
       <c r="H11" t="n">
-        <v>2.611399999999999</v>
+        <v>2.6114</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1127</v>
+        <v>1.112700000000001</v>
       </c>
       <c r="J11" t="n">
         <v>9.028099999999998</v>
@@ -1297,7 +1297,7 @@
         <v>-5.303999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8116999999999999</v>
+        <v>-0.8117000000000001</v>
       </c>
       <c r="O11" t="n">
         <v>-4.4921</v>
@@ -1312,13 +1312,13 @@
         <v>10.1908</v>
       </c>
       <c r="S11" t="n">
-        <v>4.7378</v>
+        <v>5.0114</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8179</v>
+        <v>4.0915</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9198999999999999</v>
+        <v>0.9201</v>
       </c>
       <c r="V11" t="n">
         <v>-11.959</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.5937</v>
+        <v>8.6305</v>
       </c>
       <c r="E12" t="n">
-        <v>6.9455</v>
+        <v>7.4351</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6482</v>
+        <v>1.1953</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4187</v>
@@ -1390,13 +1390,13 @@
         <v>2.4087</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.338</v>
+        <v>-0.3013</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.292</v>
+        <v>-0.8024</v>
       </c>
       <c r="U12" t="n">
-        <v>0.954</v>
+        <v>0.5011</v>
       </c>
       <c r="V12" t="n">
         <v>7.8681</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>J. REMESAL LEON</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.878</v>
+        <v>2.029</v>
       </c>
       <c r="E13" t="n">
-        <v>3.1157</v>
+        <v>2.9184</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2377</v>
+        <v>-0.8894</v>
       </c>
       <c r="G13" t="n">
-        <v>1.29</v>
+        <v>1.4335</v>
       </c>
       <c r="H13" t="n">
-        <v>2.3851</v>
+        <v>2.3044</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.0951</v>
+        <v>-0.8709</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0725</v>
+        <v>2.6709</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0311</v>
+        <v>3.2502</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0415</v>
+        <v>-0.5793</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7826</v>
+        <v>-1.2374</v>
       </c>
       <c r="N13" t="n">
-        <v>0.354</v>
+        <v>-0.9458</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1366</v>
+        <v>-0.2915</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.594</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2736</v>
+        <v>-1.1064</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7287</v>
+        <v>-0.4337</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4551</v>
+        <v>-0.6728</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3144</v>
+        <v>1.8872</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>3.4605</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3564</v>
+        <v>1.9945</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0313</v>
+        <v>3.276</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3251</v>
+        <v>-1.2815</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.2504</v>
+        <v>4.6622</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.9371</v>
+        <v>1.2291</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3133</v>
+        <v>3.4331</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.0329</v>
+        <v>5.763</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.7486</v>
+        <v>1.2319</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7157</v>
+        <v>4.5311</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2175</v>
+        <v>-1.1008</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1885</v>
+        <v>-0.0028</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.029</v>
+        <v>-1.098</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5558999999999999</v>
+        <v>-2.0382</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9264</v>
+        <v>-3.7057</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4823</v>
+        <v>1.6676</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5332</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7884</v>
+        <v>-0.0401</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2552</v>
+        <v>-0.5895</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5177</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2022</v>
+        <v>1.2589</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3155</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1676</v>
+        <v>1.8453</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1781</v>
+        <v>2.8219</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0105</v>
+        <v>-0.9766</v>
       </c>
       <c r="G15" t="n">
-        <v>4.6622</v>
+        <v>1.29</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2291</v>
+        <v>2.3851</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4331</v>
+        <v>-1.0951</v>
       </c>
       <c r="J15" t="n">
-        <v>5.763</v>
+        <v>2.0725</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2319</v>
+        <v>2.0311</v>
       </c>
       <c r="L15" t="n">
-        <v>4.5311</v>
+        <v>0.0415</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1008</v>
+        <v>-0.7826</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0028</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.098</v>
+        <v>-1.1366</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4564</v>
+        <v>0.2409</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.138</v>
+        <v>0.4349</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3184</v>
+        <v>-0.194</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. REMESAL LEON</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8361</v>
+        <v>0.8496</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2329</v>
+        <v>0.5416</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3968</v>
+        <v>0.3079</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4335</v>
+        <v>-2.2504</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3044</v>
+        <v>-1.9371</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8709</v>
+        <v>-0.3133</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6709</v>
+        <v>-1.0329</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2502</v>
+        <v>-1.7486</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5793</v>
+        <v>0.7157</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2374</v>
+        <v>-1.2175</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9458</v>
+        <v>-0.1885</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2915</v>
+        <v>-1.029</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1853</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R17" t="n">
-        <v>2.594</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.2993</v>
+        <v>0.0264</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1192</v>
+        <v>0.2988</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1801</v>
+        <v>-0.2724</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8872</v>
+        <v>2.5177</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4605</v>
+        <v>2.2022</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.5733</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5077</v>
+        <v>-0.3525</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1094</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3983</v>
+        <v>-0.2431</v>
       </c>
       <c r="G18" t="n">
         <v>-0.2841</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2236</v>
+        <v>-0.0684</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1142</v>
+        <v>0.041</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>J. PINA GUISADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1766</v>
+        <v>-0.7788</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1974</v>
+        <v>0.3444</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9792</v>
+        <v>-1.1232</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5362</v>
+        <v>-1.2616</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8374</v>
+        <v>-0.036</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6989</v>
+        <v>-1.2257</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0215</v>
+        <v>0.1274</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0215</v>
+        <v>0.0859</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5577</v>
+        <v>-1.389</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8589</v>
+        <v>-0.1219</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6989</v>
+        <v>-1.2671</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0109</v>
+        <v>0.1673</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2189</v>
+        <v>0.217</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2079</v>
+        <v>-0.0497</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.227</v>
+        <v>-0.9252</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9996</v>
+        <v>-0.8037</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2274</v>
+        <v>-0.1215</v>
       </c>
       <c r="G20" t="n">
         <v>-1.5811</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5723</v>
+        <v>-0.2705</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4377</v>
+        <v>-0.2419</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1346</v>
+        <v>-0.0286</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PINA GUISADO</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2776</v>
+        <v>-1.2751</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1485</v>
+        <v>-0.1974</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4261</v>
+        <v>-1.0777</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2616</v>
+        <v>-1.5362</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.036</v>
+        <v>-0.8374</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2257</v>
+        <v>-0.6989</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1274</v>
+        <v>0.0215</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0859</v>
+        <v>0.0215</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0415</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.389</v>
+        <v>-1.5577</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1219</v>
+        <v>-0.8589</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2671</v>
+        <v>-0.6989</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3315</v>
+        <v>-0.1094</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0211</v>
+        <v>-0.2189</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3527</v>
+        <v>0.1094</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1188</v>
+        <v>-1.9573</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6994</v>
+        <v>-1.5035</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4195</v>
+        <v>-0.4538</v>
       </c>
       <c r="G22" t="n">
         <v>-2.1172</v>
@@ -2170,13 +2170,13 @@
         <v>2.594</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7068</v>
+        <v>-0.5453</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5969</v>
+        <v>-0.401</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.11</v>
+        <v>-0.1443</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8888</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2139</v>
+        <v>-2.7912</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3724</v>
+        <v>-5.4496</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1585</v>
+        <v>2.6584</v>
       </c>
       <c r="G23" t="n">
         <v>-2.6266</v>
@@ -2248,13 +2248,13 @@
         <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3942</v>
+        <v>-0.1831</v>
       </c>
       <c r="T23" t="n">
-        <v>1.4537</v>
+        <v>0.3765</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0595</v>
+        <v>-0.5596</v>
       </c>
       <c r="V23" t="n">
         <v>0.945</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.276399999999999</v>
+        <v>8.234999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>10.24</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.9637</v>
+        <v>-2.005200000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.723999999999999</v>
+        <v>-3.724</v>
       </c>
       <c r="H24" t="n">
         <v>-2.6114</v>
@@ -2308,7 +2308,7 @@
         <v>4.4923</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.028199999999998</v>
+        <v>-9.0282</v>
       </c>
       <c r="N24" t="n">
         <v>-3.4232</v>
@@ -2326,13 +2326,13 @@
         <v>12.97</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.737800000000001</v>
+        <v>-2.7793</v>
       </c>
       <c r="T24" t="n">
         <v>-0.9201999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.8179</v>
+        <v>-1.8594</v>
       </c>
       <c r="V24" t="n">
         <v>11.9591</v>
